--- a/Web/TestCases/Userhome.xlsx
+++ b/Web/TestCases/Userhome.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A999E9C0-54EE-424C-8865-36EDE467CEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF24AB4-21ED-4E2E-9C67-6CE8E654488C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="26850" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,20 +52,20 @@
     <t>UserHome</t>
   </si>
   <si>
-    <t>The user sees the user home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user sees the user home
+    <t>https://drive.google.com/file/d/1VCvDsCvq5V6uO6C9qZ5oM-ufmrNlQtus/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Users page home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the user page home
 </t>
   </si>
   <si>
-    <t>1. The user home is correctly.</t>
-  </si>
-  <si>
-    <t>The user home has several words in another language.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VCvDsCvq5V6uO6C9qZ5oM-ufmrNlQtus/view?usp=drive_link</t>
+    <t>1. The user page home is correctly.</t>
+  </si>
+  <si>
+    <t>The user page home has several words in another language.</t>
   </si>
 </sst>
 </file>
@@ -530,22 +530,22 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">

--- a/Web/TestCases/Userhome.xlsx
+++ b/Web/TestCases/Userhome.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF24AB4-21ED-4E2E-9C67-6CE8E654488C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1202C7-F7E7-43A1-8775-220DC98E54FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="26850" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Num</t>
   </si>
@@ -49,13 +49,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>UserHome</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1VCvDsCvq5V6uO6C9qZ5oM-ufmrNlQtus/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Users page home</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user sees the user page home
@@ -66,13 +60,73 @@
   </si>
   <si>
     <t>The user page home has several words in another language.</t>
+  </si>
+  <si>
+    <t>User page home</t>
+  </si>
+  <si>
+    <t>User config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the icon with his letter
+2. Clicks "Configuración"
+3. Modify fields in "Preferencias de usuario"
+4. Clicks "Guardar cambios"
+</t>
+  </si>
+  <si>
+    <t>1. The user data are updated.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TSFIu9UHiomFtGxdKr7_clwl86SHHSL_/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>An error is shown</t>
+  </si>
+  <si>
+    <t>UH001</t>
+  </si>
+  <si>
+    <t>UH002</t>
+  </si>
+  <si>
+    <t>UH003</t>
+  </si>
+  <si>
+    <t>UH004</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the icon with his letter
+2. Clicks "Cerrar sesión"
+</t>
+  </si>
+  <si>
+    <t>1. The user is logged out</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>1. The info "Conectado como:
+XXX" is shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the icon with his letter
+2. The info about the user is shown
+</t>
+  </si>
+  <si>
+    <t>Logged-in user information</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +150,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -137,7 +197,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -157,15 +217,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -180,6 +243,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -527,75 +604,114 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="6"/>
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="H5" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
